--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260504_205959.xlsx
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
